--- a/techweek_signed_up_transport_schedule.xlsx
+++ b/techweek_signed_up_transport_schedule.xlsx
@@ -277,7 +277,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -287,7 +287,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-6408-REFERENCE</t>
+          <t xml:space="preserve">TW-6408-SCHEDULE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -337,7 +337,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-6408] [PENDING PRIMARY] Beyond the Spec Masterclass: Engineering in the Age of Agents</t>
+          <t xml:space="preserve">[TW-6408] [PENDING] Beyond the Spec Masterclass: Engineering in the Age of Agents</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -414,92 +414,92 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-6408</t>
+          <t xml:space="preserve">TW-44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-6408-SCHEDULE</t>
+          <t xml:space="preserve">TW-44-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FHiuNwzr13e3YBI4ssUX</t>
+          <t xml:space="preserve">xowd9F3kB7mPFN1luUwY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6408</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 14:00</t>
+          <t xml:space="preserve">2026-06-01 15:50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 15:00</t>
+          <t xml:space="preserve">2026-06-01 16:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 14:00</t>
+          <t xml:space="preserve">2026-06-01 15:50</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 15:00</t>
+          <t xml:space="preserve">2026-06-01 16:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-6408] [PENDING] Beyond the Spec Masterclass: Engineering in the Age of Agents</t>
+          <t xml:space="preserve">[TW-44-TRAVEL-IN] Beyond the Spec Masterclass: Engineering in the Age of Agents -&gt; From Vibe Coding to AI-Driven Development</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flatiron</t>
+          <t xml:space="preserve">Beyond the Spec Masterclass: Engineering in the Age of Agents -&gt; WeWork, 135 Madison Ave, New York, NY</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM One Madison Avenue, 1 Madison Ave,, New York, NY 10010</t>
+          <t xml:space="preserve">Beyond the Spec Masterclass: Engineering in the Age of Agents -&gt; WeWork, 135 Madison Ave, New York, NY</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">walk</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk approx 10 min / 767 m using OSM-geocoded points.</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -514,27 +514,27 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/FHiuNwzr13e3YBI4ssUX</t>
+          <t xml:space="preserve">https://partiful.com/e/xowd9F3kB7mPFN1luUwY</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-44-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-44-SCHEDULE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -561,77 +561,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">event</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">primary</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 15:50</t>
+          <t xml:space="preserve">2026-06-01 16:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-01 17:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-01 16:00</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01 15:50</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 16:00</t>
+          <t xml:space="preserve">2026-06-01 17:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-44-TRAVEL-IN] Beyond the Spec Masterclass: Engineering in the Age of Agents -&gt; From Vibe Coding to AI-Driven Development</t>
+          <t xml:space="preserve">[TW-44] [PENDING] From Vibe Coding to AI-Driven Development</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyond the Spec Masterclass: Engineering in the Age of Agents -&gt; WeWork, 135 Madison Ave, New York, NY</t>
+          <t xml:space="preserve">WeWork, 135 Madison Ave, New York, NY</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyond the Spec Masterclass: Engineering in the Age of Agents -&gt; WeWork, 135 Madison Ave, New York, NY</t>
+          <t xml:space="preserve">WeWork, 135 Madison Ave, New York, NY</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">exact_from_signup_status</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">walk</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk approx 10 min / 767 m using OSM-geocoded points.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -646,22 +646,22 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">71</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-44</t>
+          <t xml:space="preserve">TW-5110</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-44-REFERENCE</t>
+          <t xml:space="preserve">TW-5110-REFERENCE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">xowd9F3kB7mPFN1luUwY</t>
+          <t xml:space="preserve">dmFBKIxzn2LdFmktqas8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">5110</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -708,47 +708,47 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 16:00</t>
+          <t xml:space="preserve">2026-06-01 17:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-01 18:30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-01 17:00</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01 16:00</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 17:00</t>
+          <t xml:space="preserve">2026-06-01 18:30</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-44] [PENDING PRIMARY] From Vibe Coding to AI-Driven Development</t>
+          <t xml:space="preserve">[TW-5110] [PENDING BACKUP] Slack x Amplitude: AI at work</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WeWork, 135 Madison Ave, New York, NY</t>
+          <t xml:space="preserve">Tribeca</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WeWork, 135 Madison Ave, New York, NY</t>
+          <t xml:space="preserve">Fabrik, 16 Vestry St, New York, NY 10013</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_signup_status</t>
+          <t xml:space="preserve">exact_from_partiful_maps</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -778,27 +778,27 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/xowd9F3kB7mPFN1luUwY</t>
+          <t xml:space="preserve">https://partiful.com/e/dmFBKIxzn2LdFmktqas8</t>
         </is>
       </c>
     </row>
@@ -810,127 +810,127 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-44</t>
+          <t xml:space="preserve">TW-5978</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-44-SCHEDULE</t>
+          <t xml:space="preserve">TW-5978-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">xowd9F3kB7mPFN1luUwY</t>
+          <t xml:space="preserve">OF1vP5L8dtXKRtInyWKs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 16:00</t>
+          <t xml:space="preserve">2026-06-01 17:28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 17:00</t>
+          <t xml:space="preserve">2026-06-01 18:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 16:00</t>
+          <t xml:space="preserve">2026-06-01 17:28</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 17:00</t>
+          <t xml:space="preserve">2026-06-01 18:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-44] [PENDING] From Vibe Coding to AI-Driven Development</t>
+          <t xml:space="preserve">[TW-5978-TRAVEL-IN] From Vibe Coding to AI-Driven Development -&gt; Open Source Must Win</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">WeWork, 135 Madison Ave, New York, NY</t>
+          <t xml:space="preserve">From Vibe Coding to AI-Driven Development -&gt; Lower East Side</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">WeWork, 135 Madison Ave, New York, NY</t>
+          <t xml:space="preserve">From Vibe Coding to AI-Driven Development -&gt; Lower East Side</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_signup_status</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 3 min to 33 St (4/6); subway 23 min; walk 1 min from Delancey St-Essex St (F); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">4 33 St to Canal St; J Canal St to Delancey St-Essex St</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/xowd9F3kB7mPFN1luUwY</t>
+          <t xml:space="preserve">https://partiful.com/e/OF1vP5L8dtXKRtInyWKs?c=s6u4EYds</t>
         </is>
       </c>
     </row>
@@ -942,22 +942,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5110</t>
+          <t xml:space="preserve">TW-5962</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5110-REFERENCE</t>
+          <t xml:space="preserve">TW-5962-REFERENCE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dmFBKIxzn2LdFmktqas8</t>
+          <t xml:space="preserve">09a0qPKv0cSOIOSGxjTQ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5110</t>
+          <t xml:space="preserve">5962</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -977,37 +977,37 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 17:00</t>
+          <t xml:space="preserve">2026-06-01 18:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:30</t>
+          <t xml:space="preserve">2026-06-01 21:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 17:00</t>
+          <t xml:space="preserve">2026-06-01 18:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:30</t>
+          <t xml:space="preserve">2026-06-01 21:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5110] [PENDING BACKUP] Slack x Amplitude: AI at work</t>
+          <t xml:space="preserve">[TW-5962] [REG BACKUP] Software for Hardware: The Tools Powering Robotics &amp; Embodied AI</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tribeca</t>
+          <t xml:space="preserve">Civic Hall, 124 E 14th St 2nd Floor, New York, NY</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabrik, 16 Vestry St, New York, NY 10013</t>
+          <t xml:space="preserve">Civic Hall, 124 E 14th St, New York, NY 10003</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1042,27 +1042,27 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve">Partiful registered only. Secondary Luma checkout is $20 and was explicitly skipped. Partiful registered; skip paid Luma checkout Submitted via Partiful API; rsvpStatus=GOING; count=1; plusOne=none. Secondary Luma link requires $20 paid ticket; user explicitly said do not complete checkout.</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">86</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/dmFBKIxzn2LdFmktqas8</t>
+          <t xml:space="preserve">https://partiful.com/e/09a0qPKv0cSOIOSGxjTQ</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5978-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-5978-SCHEDULE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1089,107 +1089,107 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5978</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">event</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">primary</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 17:28</t>
+          <t xml:space="preserve">2026-06-01 18:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-01 21:00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-01 18:00</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01 17:28</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:00</t>
+          <t xml:space="preserve">2026-06-01 21:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5978-TRAVEL-IN] From Vibe Coding to AI-Driven Development -&gt; Open Source Must Win</t>
+          <t xml:space="preserve">[TW-5978] [PENDING] Open Source Must Win</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">From Vibe Coding to AI-Driven Development -&gt; Lower East Side</t>
+          <t xml:space="preserve">Lower East Side</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">From Vibe Coding to AI-Driven Development -&gt; Lower East Side</t>
+          <t xml:space="preserve">Delancey St Essex St, New York, NY</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">approx_neighborhood_hidden</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">subway+walk</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 3 min to 33 St (4/6); subway 23 min; walk 1 min from Delancey St-Essex St (F); includes 5 min buffer.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 33 St to Canal St; J Canal St to Delancey St-Essex St</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor delays possible</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">If this is not approved, use registered backup NYC B2B at Skinos instead. Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1206,22 +1206,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5962</t>
+          <t xml:space="preserve">TW-4200</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5962-REFERENCE</t>
+          <t xml:space="preserve">TW-4200-REFERENCE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">09a0qPKv0cSOIOSGxjTQ</t>
+          <t xml:space="preserve">oQvmxTsHOVayx47ok3li</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5962</t>
+          <t xml:space="preserve">4200</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1241,42 +1241,42 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:00</t>
+          <t xml:space="preserve">2026-06-01 18:30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:00</t>
+          <t xml:space="preserve">2026-06-01 20:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:00</t>
+          <t xml:space="preserve">2026-06-01 18:30</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:00</t>
+          <t xml:space="preserve">2026-06-01 20:00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5962] [REG BACKUP] Software for Hardware: The Tools Powering Robotics &amp; Embodied AI</t>
+          <t xml:space="preserve">[TW-4200] [REG BACKUP] NYC B2B: AI Founders &amp; Investors Mixer</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civic Hall, 124 E 14th St 2nd Floor, New York, NY</t>
+          <t xml:space="preserve">Skinos, 123 Washington St, New York, NY</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Civic Hall, 124 E 14th St, New York, NY 10003</t>
+          <t xml:space="preserve">Skinos, 123 Washington St, New York, NY</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
+          <t xml:space="preserve">exact_from_signup_status</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1306,34 +1306,34 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partiful registered only. Secondary Luma checkout is $20 and was explicitly skipped. Partiful registered; skip paid Luma checkout Submitted via Partiful API; rsvpStatus=GOING; count=1; plusOne=none. Secondary Luma link requires $20 paid ticket; user explicitly said do not complete checkout.</t>
+          <t xml:space="preserve">Registered backup near FiDi. Use if Open Source Must Win is not approved or is too low signal in practice. Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">169</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/09a0qPKv0cSOIOSGxjTQ</t>
+          <t xml:space="preserve">https://partiful.com/e/oQvmxTsHOVayx47ok3li?c=0hT1WkMm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5978-REFERENCE</t>
+          <t xml:space="preserve">TW-20260601-TRAVEL-HOME</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1353,77 +1353,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5978</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:00</t>
+          <t xml:space="preserve">2026-06-01 21:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-01 21:35</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-01 21:00</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01 18:00</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:00</t>
+          <t xml:space="preserve">2026-06-01 21:35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5978] [PENDING PRIMARY] Open Source Must Win</t>
+          <t xml:space="preserve">[TW-20260601-TRAVEL-HOME] Open Source Must Win -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lower East Side</t>
+          <t xml:space="preserve">Open Source Must Win -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delancey St Essex St, New York, NY</t>
+          <t xml:space="preserve">Open Source Must Win -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">walk</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk approx 35 min / 2751 m using OSM-geocoded points.</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1438,22 +1438,22 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t xml:space="preserve">If this is not approved, use registered backup NYC B2B at Skinos instead. Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1470,154 +1470,154 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5978</t>
+          <t xml:space="preserve">TW-4551</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5978-SCHEDULE</t>
+          <t xml:space="preserve">TW-4551-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">OF1vP5L8dtXKRtInyWKs</t>
+          <t xml:space="preserve">M7pXmV8sOXT11yHb9pKw</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5978</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:00</t>
+          <t xml:space="preserve">2026-06-02 11:13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:00</t>
+          <t xml:space="preserve">2026-06-02 12:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:00</t>
+          <t xml:space="preserve">2026-06-02 11:13</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:00</t>
+          <t xml:space="preserve">2026-06-02 12:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5978] [PENDING] Open Source Must Win</t>
+          <t xml:space="preserve">[TW-4551-TRAVEL-IN] FiDi home base -&gt; How to Write a Book on AI in Enterprise SDLC While Patterns Keep Changing</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lower East Side</t>
+          <t xml:space="preserve">FiDi home base -&gt; Midtown</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delancey St Essex St, New York, NY</t>
+          <t xml:space="preserve">FiDi home base -&gt; Midtown</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 40 min; walk 2 min from 42 St-Bryant Pk (B/D/F/M); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2 Wall St to Times Sq-42 St; R Times Sq-42 St to 46 St; F 46 St to 42 St-Bryant Pk</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t xml:space="preserve">If this is not approved, use registered backup NYC B2B at Skinos instead. Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/OF1vP5L8dtXKRtInyWKs?c=s6u4EYds</t>
+          <t xml:space="preserve">https://partiful.com/e/M7pXmV8sOXT11yHb9pKw</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4200</t>
+          <t xml:space="preserve">TW-4551</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4200-REFERENCE</t>
+          <t xml:space="preserve">TW-4551-SCHEDULE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">oQvmxTsHOVayx47ok3li</t>
+          <t xml:space="preserve">M7pXmV8sOXT11yHb9pKw</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200</t>
+          <t xml:space="preserve">4551</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1627,52 +1627,52 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">primary</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:30</t>
+          <t xml:space="preserve">2026-06-02 12:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 20:00</t>
+          <t xml:space="preserve">2026-06-02 13:45</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 18:30</t>
+          <t xml:space="preserve">2026-06-02 12:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 20:00</t>
+          <t xml:space="preserve">2026-06-02 13:45</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4200] [REG BACKUP] NYC B2B: AI Founders &amp; Investors Mixer</t>
+          <t xml:space="preserve">[TW-4551] [PENDING] How to Write a Book on AI in Enterprise SDLC While Patterns Keep Changing</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skinos, 123 Washington St, New York, NY</t>
+          <t xml:space="preserve">Midtown</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skinos, 123 Washington St, New York, NY</t>
+          <t xml:space="preserve">Bryant Park, New York, NY</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_signup_status</t>
+          <t xml:space="preserve">approx_neighborhood_hidden</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1702,124 +1702,124 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registered backup near FiDi. Use if Open Source Must Win is not approved or is too low signal in practice. Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t xml:space="preserve">169</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/oQvmxTsHOVayx47ok3li?c=0hT1WkMm</t>
+          <t xml:space="preserve">https://partiful.com/e/M7pXmV8sOXT11yHb9pKw</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5978</t>
+          <t xml:space="preserve">TW-4522</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-20260601-TRAVEL-HOME</t>
+          <t xml:space="preserve">TW-4522-REFERENCE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">OF1vP5L8dtXKRtInyWKs</t>
+          <t xml:space="preserve">5vHvRPI0VlMQwOmQadCN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">4522</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">event</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">waitlisted</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:00</t>
+          <t xml:space="preserve">2026-06-02 16:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:35</t>
+          <t xml:space="preserve">2026-06-02 19:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:00</t>
+          <t xml:space="preserve">2026-06-02 16:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01 21:35</t>
+          <t xml:space="preserve">2026-06-02 19:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-20260601-TRAVEL-HOME] Open Source Must Win -&gt; FiDi home base</t>
+          <t xml:space="preserve">[TW-4522] [WAITLIST BACKUP] Operating MCP</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Source Must Win -&gt; FiDi home base</t>
+          <t xml:space="preserve">TBC</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Source Must Win -&gt; FiDi home base</t>
+          <t xml:space="preserve">Bryant Park, New York, NY</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">approx_neighborhood_hidden</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">walk</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk approx 35 min / 2751 m using OSM-geocoded points.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1834,27 +1834,27 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Monitor waitlist / host approval Submitted via Partiful API; rsvpStatus=WAITLIST; count=2; plusOne=TBD.</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">98</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/OF1vP5L8dtXKRtInyWKs?c=s6u4EYds</t>
+          <t xml:space="preserve">https://partiful.com/e/5vHvRPI0VlMQwOmQadCN</t>
         </is>
       </c>
     </row>
@@ -1866,127 +1866,127 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4551</t>
+          <t xml:space="preserve">TW-4341</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4551-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-4341-SCHEDULE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">M7pXmV8sOXT11yHb9pKw</t>
+          <t xml:space="preserve">bn5h1g13xzOV6R5XkLaE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">4341</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">event</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">primary</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 11:13</t>
+          <t xml:space="preserve">2026-06-02 16:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 12:00</t>
+          <t xml:space="preserve">2026-06-02 17:30</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 11:13</t>
+          <t xml:space="preserve">2026-06-02 16:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 12:00</t>
+          <t xml:space="preserve">2026-06-02 17:30</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4551-TRAVEL-IN] FiDi home base -&gt; How to Write a Book on AI in Enterprise SDLC While Patterns Keep Changing</t>
+          <t xml:space="preserve">[TW-4341] [PENDING] From Copilot to Control Plane - Visdom</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FiDi home base -&gt; Midtown</t>
+          <t xml:space="preserve">Midtown</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FiDi home base -&gt; Midtown</t>
+          <t xml:space="preserve">Bryant Park, New York, NY</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">approx_neighborhood_hidden</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">subway+walk</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 40 min; walk 2 min from 42 St-Bryant Pk (B/D/F/M); includes 5 min buffer.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Wall St to Times Sq-42 St; R Times Sq-42 St to 46 St; F 46 St to 42 St-Bryant Pk</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor delays possible</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/M7pXmV8sOXT11yHb9pKw</t>
+          <t xml:space="preserve">https://partiful.com/e/bn5h1g13xzOV6R5XkLaE</t>
         </is>
       </c>
     </row>
@@ -1998,22 +1998,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4551</t>
+          <t xml:space="preserve">TW-4224</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4551-REFERENCE</t>
+          <t xml:space="preserve">TW-4224-REFERENCE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">M7pXmV8sOXT11yHb9pKw</t>
+          <t xml:space="preserve">XqIBMZmB4oubCZWFP2Sl</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551</t>
+          <t xml:space="preserve">4224</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2028,42 +2028,42 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 12:00</t>
+          <t xml:space="preserve">2026-06-02 17:30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 13:45</t>
+          <t xml:space="preserve">2026-06-02 19:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 12:00</t>
+          <t xml:space="preserve">2026-06-02 17:30</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 13:45</t>
+          <t xml:space="preserve">2026-06-02 19:00</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4551] [PENDING PRIMARY] How to Write a Book on AI in Enterprise SDLC While Patterns Keep Changing</t>
+          <t xml:space="preserve">[TW-4224] [PENDING BACKUP] WorkOS + Postman Agents &amp; APIs Demo Night</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtown</t>
+          <t xml:space="preserve">56 Greene Street, 4th Floor New York, NY 10012</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryant Park, New York, NY</t>
+          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2103,49 +2103,49 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">217</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/M7pXmV8sOXT11yHb9pKw</t>
+          <t xml:space="preserve">https://partiful.com/e/XqIBMZmB4oubCZWFP2Sl</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4551</t>
+          <t xml:space="preserve">TW-5415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4551-SCHEDULE</t>
+          <t xml:space="preserve">TW-5415-REFERENCE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">M7pXmV8sOXT11yHb9pKw</t>
+          <t xml:space="preserve">UBrZopzqpRwbn6Qk0npO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551</t>
+          <t xml:space="preserve">5415</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2160,42 +2160,42 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 12:00</t>
+          <t xml:space="preserve">2026-06-02 17:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 13:45</t>
+          <t xml:space="preserve">2026-06-02 19:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 12:00</t>
+          <t xml:space="preserve">2026-06-02 17:30</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 13:45</t>
+          <t xml:space="preserve">2026-06-02 19:00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4551] [PENDING] How to Write a Book on AI in Enterprise SDLC While Patterns Keep Changing</t>
+          <t xml:space="preserve">[TW-5415] [PENDING BACKUP] AI, Algorithms &amp; Liability: What Tech Leaders &amp; Creators Need to Know</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtown</t>
+          <t xml:space="preserve">One Battery Park Plaza, 7th Floor New York, NY 10004</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryant Park, New York, NY</t>
+          <t xml:space="preserve">Wall St, New York, NY</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2235,154 +2235,154 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">72</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/M7pXmV8sOXT11yHb9pKw</t>
+          <t xml:space="preserve">https://partiful.com/e/UBrZopzqpRwbn6Qk0npO?c=4IfpVNvT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4341</t>
+          <t xml:space="preserve">TW-4161</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4341-REFERENCE</t>
+          <t xml:space="preserve">TW-4161-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">bn5h1g13xzOV6R5XkLaE</t>
+          <t xml:space="preserve">7DYGSiY1WUuRSvEnD5gp</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4341</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 16:00</t>
+          <t xml:space="preserve">2026-06-02 17:36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 16:00</t>
+          <t xml:space="preserve">2026-06-02 17:36</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4341] [PENDING PRIMARY] From Copilot to Control Plane - Visdom</t>
+          <t xml:space="preserve">[TW-4161-TRAVEL-IN] From Copilot to Control Plane - Visdom -&gt; Future of DevEx</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtown</t>
+          <t xml:space="preserve">From Copilot to Control Plane - Visdom -&gt; SoHo</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryant Park, New York, NY</t>
+          <t xml:space="preserve">From Copilot to Control Plane - Visdom -&gt; SoHo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 2 min to 42 St-Bryant Pk (B/D/F/M); subway 17 min; walk 0 min from Prince St (N/Q/R/W); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">B 42 St-Bryant Pk to DeKalb Av; Q DeKalb Av to Prince St</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/bn5h1g13xzOV6R5XkLaE</t>
+          <t xml:space="preserve">https://partiful.com/e/7DYGSiY1WUuRSvEnD5gp?c=aQ_TnSt9</t>
         </is>
       </c>
     </row>
@@ -2394,22 +2394,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4522</t>
+          <t xml:space="preserve">TW-5437</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4522-REFERENCE</t>
+          <t xml:space="preserve">TW-5437-REFERENCE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5vHvRPI0VlMQwOmQadCN</t>
+          <t xml:space="preserve">FSzOO6xPn11iqxVdtQ9j</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4522</t>
+          <t xml:space="preserve">5437</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2419,47 +2419,47 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">waitlisted</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">apply</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 16:00</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:00</t>
+          <t xml:space="preserve">2026-06-02 19:30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 16:00</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:00</t>
+          <t xml:space="preserve">2026-06-02 19:30</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4522] [WAITLIST BACKUP] Operating MCP</t>
+          <t xml:space="preserve">[TW-5437] [PENDING CURATED] Enterprise AI Happy Hour</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBC</t>
+          <t xml:space="preserve">SoHo</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryant Park, New York, NY</t>
+          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitor waitlist / host approval Submitted via Partiful API; rsvpStatus=WAITLIST; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2509,39 +2509,39 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t xml:space="preserve">98</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/5vHvRPI0VlMQwOmQadCN</t>
+          <t xml:space="preserve">https://partiful.com/e/FSzOO6xPn11iqxVdtQ9j?</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4341</t>
+          <t xml:space="preserve">TW-5925</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4341-SCHEDULE</t>
+          <t xml:space="preserve">TW-5925-REFERENCE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">bn5h1g13xzOV6R5XkLaE</t>
+          <t xml:space="preserve">jytNb4IdG0HxwJnqDSgf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4341</t>
+          <t xml:space="preserve">5925</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2556,47 +2556,47 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 16:00</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 20:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 16:00</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 20:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4341] [PENDING] From Copilot to Control Plane - Visdom</t>
+          <t xml:space="preserve">[TW-5925] [PENDING BACKUP] Cloudflare + Shopify: Build for the Agent Era</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtown</t>
+          <t xml:space="preserve">SoHo</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryant Park, New York, NY</t>
+          <t xml:space="preserve">Shopify New York, 131 Greene St, New York, NY 10012</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve">exact_from_partiful_maps</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2641,39 +2641,39 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/bn5h1g13xzOV6R5XkLaE</t>
+          <t xml:space="preserve">https://partiful.com/e/jytNb4IdG0HxwJnqDSgf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4224</t>
+          <t xml:space="preserve">TW-4161</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4224-REFERENCE</t>
+          <t xml:space="preserve">TW-4161-SCHEDULE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">XqIBMZmB4oubCZWFP2Sl</t>
+          <t xml:space="preserve">7DYGSiY1WUuRSvEnD5gp</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4224</t>
+          <t xml:space="preserve">4161</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2688,37 +2688,37 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">primary</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:00</t>
+          <t xml:space="preserve">2026-06-02 21:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 18:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:00</t>
+          <t xml:space="preserve">2026-06-02 21:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4224] [PENDING BACKUP] WorkOS + Postman Agents &amp; APIs Demo Night</t>
+          <t xml:space="preserve">[TW-4161] [PENDING] Future of DevEx</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">56 Greene Street, 4th Floor New York, NY 10012</t>
+          <t xml:space="preserve">SoHo</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2763,154 +2763,154 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t xml:space="preserve">217</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/XqIBMZmB4oubCZWFP2Sl</t>
+          <t xml:space="preserve">https://partiful.com/e/7DYGSiY1WUuRSvEnD5gp?c=aQ_TnSt9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5415</t>
+          <t xml:space="preserve">TW-4161</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5415-REFERENCE</t>
+          <t xml:space="preserve">TW-20260602-TRAVEL-HOME</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UBrZopzqpRwbn6Qk0npO</t>
+          <t xml:space="preserve">7DYGSiY1WUuRSvEnD5gp</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5415</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 21:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:00</t>
+          <t xml:space="preserve">2026-06-02 21:20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:30</t>
+          <t xml:space="preserve">2026-06-02 21:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:00</t>
+          <t xml:space="preserve">2026-06-02 21:20</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5415] [PENDING BACKUP] AI, Algorithms &amp; Liability: What Tech Leaders &amp; Creators Need to Know</t>
+          <t xml:space="preserve">[TW-20260602-TRAVEL-HOME] Future of DevEx -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">One Battery Park Plaza, 7th Floor New York, NY 10004</t>
+          <t xml:space="preserve">Future of DevEx -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wall St, New York, NY</t>
+          <t xml:space="preserve">Future of DevEx -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 0 min to Prince St (N/Q/R/W); subway 15 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N Prince St to Canal St; 4 Canal St to Wall St</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/UBrZopzqpRwbn6Qk0npO?c=4IfpVNvT</t>
+          <t xml:space="preserve">https://partiful.com/e/7DYGSiY1WUuRSvEnD5gp?c=aQ_TnSt9</t>
         </is>
       </c>
     </row>
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4161</t>
+          <t xml:space="preserve">TW-5889</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4161-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-5889-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7DYGSiY1WUuRSvEnD5gp</t>
+          <t xml:space="preserve">4HvzWY1VZlHgK21fMBUz</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2957,37 +2957,37 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:36</t>
+          <t xml:space="preserve">2026-06-03 11:29</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 12:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 17:36</t>
+          <t xml:space="preserve">2026-06-03 11:29</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 12:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4161-TRAVEL-IN] From Copilot to Control Plane - Visdom -&gt; Future of DevEx</t>
+          <t xml:space="preserve">[TW-5889-TRAVEL-IN] FiDi home base -&gt; Building secure AI for your data: DeepFellow Demo + Q&amp;A</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">From Copilot to Control Plane - Visdom -&gt; SoHo</t>
+          <t xml:space="preserve">FiDi home base -&gt; Chelsea</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">From Copilot to Control Plane - Visdom -&gt; SoHo</t>
+          <t xml:space="preserve">FiDi home base -&gt; Chelsea</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3002,17 +3002,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 2 min to 42 St-Bryant Pk (B/D/F/M); subway 17 min; walk 0 min from Prince St (N/Q/R/W); includes 5 min buffer.</t>
+          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 22 min; walk 4 min from 23 St (A/C/E); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t xml:space="preserve">B 42 St-Bryant Pk to DeKalb Av; Q DeKalb Av to Prince St</t>
+          <t xml:space="preserve">2 Wall St to 23 St</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3042,34 +3042,34 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/7DYGSiY1WUuRSvEnD5gp?c=aQ_TnSt9</t>
+          <t xml:space="preserve">https://partiful.com/e/4HvzWY1VZlHgK21fMBUz?c=g5NbnbjN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4161</t>
+          <t xml:space="preserve">TW-5889</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4161-REFERENCE</t>
+          <t xml:space="preserve">TW-5889-SCHEDULE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7DYGSiY1WUuRSvEnD5gp</t>
+          <t xml:space="preserve">4HvzWY1VZlHgK21fMBUz</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4161</t>
+          <t xml:space="preserve">5889</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3089,37 +3089,37 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 12:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:00</t>
+          <t xml:space="preserve">2026-06-03 13:15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 12:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:00</t>
+          <t xml:space="preserve">2026-06-03 13:15</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4161] [PENDING PRIMARY] Future of DevEx</t>
+          <t xml:space="preserve">[TW-5889] [PENDING] Building secure AI for your data: DeepFellow Demo + Q&amp;A</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SoHo</t>
+          <t xml:space="preserve">Chelsea</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
+          <t xml:space="preserve">23rd Street and 8th Avenue, New York, NY</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">80</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/7DYGSiY1WUuRSvEnD5gp?c=aQ_TnSt9</t>
+          <t xml:space="preserve">https://partiful.com/e/4HvzWY1VZlHgK21fMBUz?c=g5NbnbjN</t>
         </is>
       </c>
     </row>
@@ -3186,22 +3186,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5437</t>
+          <t xml:space="preserve">TW-5820</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5437-REFERENCE</t>
+          <t xml:space="preserve">TW-5820-REFERENCE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FSzOO6xPn11iqxVdtQ9j</t>
+          <t xml:space="preserve">titPml1Nw0DKwGl9B6CF</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437</t>
+          <t xml:space="preserve">5820</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3221,37 +3221,37 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 13:30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:30</t>
+          <t xml:space="preserve">2026-06-03 17:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 13:30</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 19:30</t>
+          <t xml:space="preserve">2026-06-03 17:00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5437] [PENDING CURATED] Enterprise AI Happy Hour</t>
+          <t xml:space="preserve">[TW-5820] [PENDING CURATED] Anthropic Founder Salon: Inside the AI-Native Era</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SoHo</t>
+          <t xml:space="preserve">New York, NY - Chelsea neighborhood (venue details upon confirmation)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
+          <t xml:space="preserve">23rd Street and 8th Avenue, New York, NY</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3301,144 +3301,144 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">94</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/FSzOO6xPn11iqxVdtQ9j?</t>
+          <t xml:space="preserve">https://partiful.com/e/titPml1Nw0DKwGl9B6CF</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5925</t>
+          <t xml:space="preserve">TW-4444</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5925-REFERENCE</t>
+          <t xml:space="preserve">TW-4444-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">jytNb4IdG0HxwJnqDSgf</t>
+          <t xml:space="preserve">1N6CtiCpYquktoTh5NUm</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5925</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 13:35</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 20:00</t>
+          <t xml:space="preserve">2026-06-03 14:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 13:35</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 20:00</t>
+          <t xml:space="preserve">2026-06-03 14:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5925] [PENDING BACKUP] Cloudflare + Shopify: Build for the Agent Era</t>
+          <t xml:space="preserve">[TW-4444-TRAVEL-IN] Building secure AI for your data: DeepFellow Demo + Q&amp;A -&gt; The Future of Coding Agents and IDE</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SoHo</t>
+          <t xml:space="preserve">Building secure AI for your data: DeepFellow Demo + Q&amp;A -&gt; 1155 6th Ave, New York, NY 10036</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify New York, 131 Greene St, New York, NY 10012</t>
+          <t xml:space="preserve">Building secure AI for your data: DeepFellow Demo + Q&amp;A -&gt; 1155 6th Ave, New York, NY 10036</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 4 min to 23 St (A/C/E); subway 11 min; walk 5 min from Times Sq-42 St (GS); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A 23 St to 34 St-Penn Station; 1 34 St-Penn Station to Times Sq-42 St</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/jytNb4IdG0HxwJnqDSgf</t>
+          <t xml:space="preserve">https://partiful.com/e/1N6CtiCpYquktoTh5NUm</t>
         </is>
       </c>
     </row>
@@ -3450,22 +3450,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4161</t>
+          <t xml:space="preserve">TW-4444</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4161-SCHEDULE</t>
+          <t xml:space="preserve">TW-4444-SCHEDULE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7DYGSiY1WUuRSvEnD5gp</t>
+          <t xml:space="preserve">1N6CtiCpYquktoTh5NUm</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4161</t>
+          <t xml:space="preserve">4444</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3485,42 +3485,42 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 14:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:00</t>
+          <t xml:space="preserve">2026-06-03 15:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 18:00</t>
+          <t xml:space="preserve">2026-06-03 14:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:00</t>
+          <t xml:space="preserve">2026-06-03 15:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4161] [PENDING] Future of DevEx</t>
+          <t xml:space="preserve">[TW-4444] [PENDING] The Future of Coding Agents and IDE</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SoHo</t>
+          <t xml:space="preserve">1155 6th Ave, New York, NY 10036</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
+          <t xml:space="preserve">1155 6th Ave, New York, NY 10036</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve">manual_exact_manhattan</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3550,27 +3550,27 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">72</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/7DYGSiY1WUuRSvEnD5gp?c=aQ_TnSt9</t>
+          <t xml:space="preserve">https://partiful.com/e/1N6CtiCpYquktoTh5NUm</t>
         </is>
       </c>
     </row>
@@ -3582,17 +3582,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4161</t>
+          <t xml:space="preserve">TW-5529</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-20260602-TRAVEL-HOME</t>
+          <t xml:space="preserve">TW-5529-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7DYGSiY1WUuRSvEnD5gp</t>
+          <t xml:space="preserve">E8NhJNHWGhMetLlrFvQ7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3617,37 +3617,37 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:00</t>
+          <t xml:space="preserve">2026-06-03 15:40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:20</t>
+          <t xml:space="preserve">2026-06-03 16:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:00</t>
+          <t xml:space="preserve">2026-06-03 15:40</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02 21:20</t>
+          <t xml:space="preserve">2026-06-03 16:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-20260602-TRAVEL-HOME] Future of DevEx -&gt; FiDi home base</t>
+          <t xml:space="preserve">[TW-5529-TRAVEL-IN] The Future of Coding Agents and IDE -&gt; Fireside chat - When coding agents are the user?</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Future of DevEx -&gt; FiDi home base</t>
+          <t xml:space="preserve">The Future of Coding Agents and IDE -&gt; New York, NY</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Future of DevEx -&gt; FiDi home base</t>
+          <t xml:space="preserve">The Future of Coding Agents and IDE -&gt; New York, NY</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">subway+walk</t>
+          <t xml:space="preserve">walk</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3667,17 +3667,17 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 0 min to Prince St (N/Q/R/W); subway 15 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
+          <t xml:space="preserve">Walk approx 20 min / 1595 m using OSM-geocoded points.</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t xml:space="preserve">N Prince St to Canal St; 4 Canal St to Wall St</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor delays possible</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3702,166 +3702,166 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/7DYGSiY1WUuRSvEnD5gp?c=aQ_TnSt9</t>
+          <t xml:space="preserve">https://partiful.com/e/E8NhJNHWGhMetLlrFvQ7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5889</t>
+          <t xml:space="preserve">TW-4719</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5889-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-4719-REFERENCE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4HvzWY1VZlHgK21fMBUz</t>
+          <t xml:space="preserve">2NP0rZW8BmdGAGUOEhGP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">4719</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">event</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">apply</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 11:29</t>
+          <t xml:space="preserve">2026-06-03 16:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 12:00</t>
+          <t xml:space="preserve">2026-06-03 21:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 11:29</t>
+          <t xml:space="preserve">2026-06-03 16:00</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 12:00</t>
+          <t xml:space="preserve">2026-06-03 21:00</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5889-TRAVEL-IN] FiDi home base -&gt; Building secure AI for your data: DeepFellow Demo + Q&amp;A</t>
+          <t xml:space="preserve">[TW-4719] [PENDING CURATED] Agent Harnesses: What It Takes to Make AI Agents Work in the Enterprise</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FiDi home base -&gt; Chelsea</t>
+          <t xml:space="preserve">Union Square</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FiDi home base -&gt; Chelsea</t>
+          <t xml:space="preserve">Union Square W, New York, NY 10003</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">exact_from_partiful_maps</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">subway+walk</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 22 min; walk 4 min from 23 St (A/C/E); includes 5 min buffer.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Wall St to 23 St</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor delays possible</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">97</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/4HvzWY1VZlHgK21fMBUz?c=g5NbnbjN</t>
+          <t xml:space="preserve">https://partiful.com/e/2NP0rZW8BmdGAGUOEhGP?f=1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5889</t>
+          <t xml:space="preserve">TW-5529</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5889-REFERENCE</t>
+          <t xml:space="preserve">TW-5529-SCHEDULE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4HvzWY1VZlHgK21fMBUz</t>
+          <t xml:space="preserve">E8NhJNHWGhMetLlrFvQ7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5889</t>
+          <t xml:space="preserve">5529</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3881,37 +3881,37 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 12:00</t>
+          <t xml:space="preserve">2026-06-03 16:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:15</t>
+          <t xml:space="preserve">2026-06-03 17:15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 12:00</t>
+          <t xml:space="preserve">2026-06-03 16:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:15</t>
+          <t xml:space="preserve">2026-06-03 17:15</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5889] [PENDING PRIMARY] Building secure AI for your data: DeepFellow Demo + Q&amp;A</t>
+          <t xml:space="preserve">[TW-5529] [REG] Fireside chat - When coding agents are the user?</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chelsea</t>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">23rd Street and 8th Avenue, New York, NY</t>
+          <t xml:space="preserve">28th Street and Broadway, New York, NY</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve">Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3961,39 +3961,39 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t xml:space="preserve">80</t>
+          <t xml:space="preserve">81</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/4HvzWY1VZlHgK21fMBUz?c=g5NbnbjN</t>
+          <t xml:space="preserve">https://partiful.com/e/E8NhJNHWGhMetLlrFvQ7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5889</t>
+          <t xml:space="preserve">TW-4778</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5889-SCHEDULE</t>
+          <t xml:space="preserve">TW-4778-REFERENCE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4HvzWY1VZlHgK21fMBUz</t>
+          <t xml:space="preserve">h1hGv0PkskcagJOv5M9K</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5889</t>
+          <t xml:space="preserve">4778</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4008,42 +4008,42 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">apply</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 12:00</t>
+          <t xml:space="preserve">2026-06-03 17:30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:15</t>
+          <t xml:space="preserve">2026-06-03 19:30</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 12:00</t>
+          <t xml:space="preserve">2026-06-03 17:30</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:15</t>
+          <t xml:space="preserve">2026-06-03 19:30</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5889] [PENDING] Building secure AI for your data: DeepFellow Demo + Q&amp;A</t>
+          <t xml:space="preserve">[TW-4778] [PENDING CURATED] The CTO Mixer: Humanizing Tech | Happy Hour</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chelsea</t>
+          <t xml:space="preserve">Midtown, Manhattan, New York, NY</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">23rd Street and 8th Avenue, New York, NY</t>
+          <t xml:space="preserve">Astor Place, New York, NY</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t xml:space="preserve">80</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/4HvzWY1VZlHgK21fMBUz?c=g5NbnbjN</t>
+          <t xml:space="preserve">https://partiful.com/e/h1hGv0PkskcagJOv5M9K</t>
         </is>
       </c>
     </row>
@@ -4110,22 +4110,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5820</t>
+          <t xml:space="preserve">TW-5693</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5820-REFERENCE</t>
+          <t xml:space="preserve">TW-5693-REFERENCE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">titPml1Nw0DKwGl9B6CF</t>
+          <t xml:space="preserve">Fp5STyPH0McEt0awlWFD</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5820</t>
+          <t xml:space="preserve">5693</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4140,47 +4140,47 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:30</t>
+          <t xml:space="preserve">2026-06-03 17:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:00</t>
+          <t xml:space="preserve">2026-06-03 19:30</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:30</t>
+          <t xml:space="preserve">2026-06-03 17:30</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:00</t>
+          <t xml:space="preserve">2026-06-03 19:30</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5820] [PENDING CURATED] Anthropic Founder Salon: Inside the AI-Native Era</t>
+          <t xml:space="preserve">[TW-5693] [PENDING BACKUP] Camp AI: Agents at Work</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York, NY - Chelsea neighborhood (venue details upon confirmation)</t>
+          <t xml:space="preserve">620 8th Ave, New York, NY 10018</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">23rd Street and 8th Avenue, New York, NY</t>
+          <t xml:space="preserve">620 8th Ave, New York, NY 10018</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve">manual_exact_manhattan</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API after user confirmed age 21+; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t xml:space="preserve">94</t>
+          <t xml:space="preserve">78</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/titPml1Nw0DKwGl9B6CF</t>
+          <t xml:space="preserve">https://partiful.com/e/Fp5STyPH0McEt0awlWFD</t>
         </is>
       </c>
     </row>
@@ -4242,17 +4242,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4444</t>
+          <t xml:space="preserve">TW-4664</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4444-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-4664-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1N6CtiCpYquktoTh5NUm</t>
+          <t xml:space="preserve">6ZuudQBBZXcMNjdMynJ2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4277,37 +4277,37 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:35</t>
+          <t xml:space="preserve">2026-06-03 17:40</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 14:00</t>
+          <t xml:space="preserve">2026-06-03 18:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 13:35</t>
+          <t xml:space="preserve">2026-06-03 17:40</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 14:00</t>
+          <t xml:space="preserve">2026-06-03 18:00</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4444-TRAVEL-IN] Building secure AI for your data: DeepFellow Demo + Q&amp;A -&gt; The Future of Coding Agents and IDE</t>
+          <t xml:space="preserve">[TW-4664-TRAVEL-IN] Fireside chat - When coding agents are the user? -&gt; MCP in the Wild: Panel &amp; Night of Networking</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Building secure AI for your data: DeepFellow Demo + Q&amp;A -&gt; 1155 6th Ave, New York, NY 10036</t>
+          <t xml:space="preserve">Fireside chat - When coding agents are the user? -&gt; East Village</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Building secure AI for your data: DeepFellow Demo + Q&amp;A -&gt; 1155 6th Ave, New York, NY 10036</t>
+          <t xml:space="preserve">Fireside chat - When coding agents are the user? -&gt; East Village</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4322,17 +4322,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 4 min to 23 St (A/C/E); subway 11 min; walk 5 min from Times Sq-42 St (GS); includes 5 min buffer.</t>
+          <t xml:space="preserve">Walk 1 min to 28 St (N/Q/R/W); subway 13 min; walk 1 min from Astor Pl (4/6); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t xml:space="preserve">A 23 St to 34 St-Penn Station; 1 34 St-Penn Station to Times Sq-42 St</t>
+          <t xml:space="preserve">N 28 St to 14 St-Union Sq; 4 14 St-Union Sq to Astor Pl</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4362,34 +4362,34 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/1N6CtiCpYquktoTh5NUm</t>
+          <t xml:space="preserve">https://partiful.com/events/6ZuudQBBZXcMNjdMynJ2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4444</t>
+          <t xml:space="preserve">TW-4664</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4444-REFERENCE</t>
+          <t xml:space="preserve">TW-4664-SCHEDULE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1N6CtiCpYquktoTh5NUm</t>
+          <t xml:space="preserve">6ZuudQBBZXcMNjdMynJ2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4444</t>
+          <t xml:space="preserve">4664</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4409,42 +4409,42 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 14:00</t>
+          <t xml:space="preserve">2026-06-03 18:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 15:00</t>
+          <t xml:space="preserve">2026-06-03 20:30</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 14:00</t>
+          <t xml:space="preserve">2026-06-03 18:00</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 15:00</t>
+          <t xml:space="preserve">2026-06-03 20:30</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4444] [PENDING PRIMARY] The Future of Coding Agents and IDE</t>
+          <t xml:space="preserve">[TW-4664] [PENDING] MCP in the Wild: Panel &amp; Night of Networking</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155 6th Ave, New York, NY 10036</t>
+          <t xml:space="preserve">East Village</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155 6th Ave, New York, NY 10036</t>
+          <t xml:space="preserve">Astor Place, New York, NY</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">manual_exact_manhattan</t>
+          <t xml:space="preserve">approx_neighborhood_hidden</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4489,39 +4489,39 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/1N6CtiCpYquktoTh5NUm</t>
+          <t xml:space="preserve">https://partiful.com/events/6ZuudQBBZXcMNjdMynJ2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4444</t>
+          <t xml:space="preserve">TW-4197</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4444-SCHEDULE</t>
+          <t xml:space="preserve">TW-4197-REFERENCE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1N6CtiCpYquktoTh5NUm</t>
+          <t xml:space="preserve">UhyErPPxuo2vELIutdGj</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4444</t>
+          <t xml:space="preserve">4197</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4536,47 +4536,47 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">apply</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 14:00</t>
+          <t xml:space="preserve">2026-06-03 19:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 15:00</t>
+          <t xml:space="preserve">2026-06-03 21:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 14:00</t>
+          <t xml:space="preserve">2026-06-03 19:00</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 15:00</t>
+          <t xml:space="preserve">2026-06-03 21:00</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4444] [PENDING] The Future of Coding Agents and IDE</t>
+          <t xml:space="preserve">[TW-4197] [PENDING CURATED] The Tech Leaders Suite</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155 6th Ave, New York, NY 10036</t>
+          <t xml:space="preserve">Brooklyn</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155 6th Ave, New York, NY 10036</t>
+          <t xml:space="preserve">Barclays Center, Brooklyn, NY</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">manual_exact_manhattan</t>
+          <t xml:space="preserve">approx_neighborhood_hidden</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4606,27 +4606,27 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/1N6CtiCpYquktoTh5NUm</t>
+          <t xml:space="preserve">https://partiful.com/e/UhyErPPxuo2vELIutdGj?</t>
         </is>
       </c>
     </row>
@@ -4638,17 +4638,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5529</t>
+          <t xml:space="preserve">TW-4664</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5529-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-20260603-TRAVEL-HOME</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8NhJNHWGhMetLlrFvQ7</t>
+          <t xml:space="preserve">6ZuudQBBZXcMNjdMynJ2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4673,37 +4673,37 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 15:40</t>
+          <t xml:space="preserve">2026-06-03 20:30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-03 20:50</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 15:40</t>
+          <t xml:space="preserve">2026-06-03 20:30</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-03 20:50</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5529-TRAVEL-IN] The Future of Coding Agents and IDE -&gt; Fireside chat - When coding agents are the user?</t>
+          <t xml:space="preserve">[TW-20260603-TRAVEL-HOME] MCP in the Wild: Panel &amp; Night of Networking -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Future of Coding Agents and IDE -&gt; New York, NY</t>
+          <t xml:space="preserve">MCP in the Wild: Panel &amp; Night of Networking -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Future of Coding Agents and IDE -&gt; New York, NY</t>
+          <t xml:space="preserve">MCP in the Wild: Panel &amp; Night of Networking -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">walk</t>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk approx 20 min / 1595 m using OSM-geocoded points.</t>
+          <t xml:space="preserve">Walk 1 min to Astor Pl (4/6); subway 14 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">4 Astor Pl to Wall St</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4758,166 +4758,166 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/E8NhJNHWGhMetLlrFvQ7</t>
+          <t xml:space="preserve">https://partiful.com/events/6ZuudQBBZXcMNjdMynJ2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4719</t>
+          <t xml:space="preserve">TW-5372</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4719-REFERENCE</t>
+          <t xml:space="preserve">TW-5372-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2NP0rZW8BmdGAGUOEhGP</t>
+          <t xml:space="preserve">5K5c4eODrGPKME7or20H</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4719</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-04 15:36</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 21:00</t>
+          <t xml:space="preserve">2026-06-04 16:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-04 15:36</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 21:00</t>
+          <t xml:space="preserve">2026-06-04 16:00</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4719] [PENDING CURATED] Agent Harnesses: What It Takes to Make AI Agents Work in the Enterprise</t>
+          <t xml:space="preserve">[TW-5372-TRAVEL-IN] FiDi home base -&gt; Shipping Faster with AI Coding Agents: What's Working and What's Not</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Union Square</t>
+          <t xml:space="preserve">FiDi home base -&gt; New York, NY</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Union Square W, New York, NY 10003</t>
+          <t xml:space="preserve">FiDi home base -&gt; New York, NY</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 19 min; walk 0 min from Prince St (N/Q/R/W); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2 Wall St to Canal St; Q Canal St to Prince St</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t xml:space="preserve">97</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/2NP0rZW8BmdGAGUOEhGP?f=1</t>
+          <t xml:space="preserve">https://partiful.com/e/5K5c4eODrGPKME7or20H</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5529</t>
+          <t xml:space="preserve">TW-5372</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5529-REFERENCE</t>
+          <t xml:space="preserve">TW-5372-SCHEDULE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8NhJNHWGhMetLlrFvQ7</t>
+          <t xml:space="preserve">5K5c4eODrGPKME7or20H</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529</t>
+          <t xml:space="preserve">5372</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4937,27 +4937,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-04 16:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:15</t>
+          <t xml:space="preserve">2026-06-04 18:51</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-04 16:00</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:15</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5529] [REG PRIMARY] Fireside chat - When coding agents are the user?</t>
+          <t xml:space="preserve">[TW-5372] [PENDING] Shipping Faster with AI Coding Agents: What's Working and What's Not</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">28th Street and Broadway, New York, NY</t>
+          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve">Leave early if needed so you can make the registered 19:00 Stop Making AI Guess event. Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none. Route calendar shortens this from the event's scheduled 19:00 end; leave 9 min early for transit.</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -5017,39 +5017,39 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t xml:space="preserve">81</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/E8NhJNHWGhMetLlrFvQ7</t>
+          <t xml:space="preserve">https://partiful.com/e/5K5c4eODrGPKME7or20H</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5529</t>
+          <t xml:space="preserve">TW-4191</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5529-SCHEDULE</t>
+          <t xml:space="preserve">TW-4191-REFERENCE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8NhJNHWGhMetLlrFvQ7</t>
+          <t xml:space="preserve">6BlGFmwIdpyndqyLYS2v</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529</t>
+          <t xml:space="preserve">4191</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5059,47 +5059,47 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-04 18:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:15</t>
+          <t xml:space="preserve">2026-06-04 20:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 16:00</t>
+          <t xml:space="preserve">2026-06-04 18:00</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:15</t>
+          <t xml:space="preserve">2026-06-04 20:00</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5529] [REG] Fireside chat - When coding agents are the user?</t>
+          <t xml:space="preserve">[TW-4191] [PENDING BACKUP] Agents at Scale</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">SoHo</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">28th Street and Broadway, New York, NY</t>
+          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t xml:space="preserve">81</t>
+          <t xml:space="preserve">93</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/E8NhJNHWGhMetLlrFvQ7</t>
+          <t xml:space="preserve">https://partiful.com/e/6BlGFmwIdpyndqyLYS2v?c=bv5YqCoL</t>
         </is>
       </c>
     </row>
@@ -5166,22 +5166,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4778</t>
+          <t xml:space="preserve">TW-4826</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4778-REFERENCE</t>
+          <t xml:space="preserve">TW-4826-REFERENCE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">h1hGv0PkskcagJOv5M9K</t>
+          <t xml:space="preserve">sGvp4VIr3KrGqRoWCKhV</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778</t>
+          <t xml:space="preserve">4826</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5196,47 +5196,47 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:30</t>
+          <t xml:space="preserve">2026-06-04 18:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 19:30</t>
+          <t xml:space="preserve">2026-06-04 19:30</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:30</t>
+          <t xml:space="preserve">2026-06-04 18:00</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 19:30</t>
+          <t xml:space="preserve">2026-06-04 19:30</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4778] [PENDING CURATED] The CTO Mixer: Humanizing Tech | Happy Hour</t>
+          <t xml:space="preserve">[TW-4826] [PENDING BACKUP] Steal These AI Workflows: Live Demos from NYC's Top AI Builders</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midtown, Manhattan, New York, NY</t>
+          <t xml:space="preserve">Union Square</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astor Place, New York, NY</t>
+          <t xml:space="preserve">Union Square E, New York, NY 10003</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve">exact_from_partiful_maps</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5266,27 +5266,27 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none. Secondary Google Form submitted for UbiquityOS Accolades build demo.</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/h1hGv0PkskcagJOv5M9K</t>
+          <t xml:space="preserve">https://partiful.com/e/sGvp4VIr3KrGqRoWCKhV</t>
         </is>
       </c>
     </row>
@@ -5298,22 +5298,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5693</t>
+          <t xml:space="preserve">TW-4183</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5693-REFERENCE</t>
+          <t xml:space="preserve">TW-4183-REFERENCE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fp5STyPH0McEt0awlWFD</t>
+          <t xml:space="preserve">bETmU06uq4TtORng6I1l</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5693</t>
+          <t xml:space="preserve">4183</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5328,47 +5328,47 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">apply</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:30</t>
+          <t xml:space="preserve">2026-06-04 18:30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 19:30</t>
+          <t xml:space="preserve">2026-06-04 21:30</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:30</t>
+          <t xml:space="preserve">2026-06-04 18:30</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 19:30</t>
+          <t xml:space="preserve">2026-06-04 21:30</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5693] [PENDING BACKUP] Camp AI: Agents at Work</t>
+          <t xml:space="preserve">[TW-4183] [PENDING CURATED] Engineering Leaders After Hours: A Build and Ship Cocktail Competition</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">620 8th Ave, New York, NY 10018</t>
+          <t xml:space="preserve">BarChef NYC, 21 W 35th St,, New York, NY</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">620 8th Ave, New York, NY 10018</t>
+          <t xml:space="preserve">BarChef NYC, 21 W 35th St,, New York, NY</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">manual_exact_manhattan</t>
+          <t xml:space="preserve">exact_from_signup_status</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API after user confirmed age 21+; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/Fp5STyPH0McEt0awlWFD</t>
+          <t xml:space="preserve">https://partiful.com/e/bETmU06uq4TtORng6I1l</t>
         </is>
       </c>
     </row>
@@ -5430,17 +5430,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4664</t>
+          <t xml:space="preserve">TW-5114</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4664-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-5114-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">X0u5GrmzvIUTrjoAOgVm</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5465,37 +5465,37 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:40</t>
+          <t xml:space="preserve">2026-06-04 18:51</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 18:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 17:40</t>
+          <t xml:space="preserve">2026-06-04 18:51</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 18:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4664-TRAVEL-IN] Fireside chat - When coding agents are the user? -&gt; MCP in the Wild: Panel &amp; Night of Networking</t>
+          <t xml:space="preserve">[TW-5114-TRAVEL-IN] Shipping Faster with AI Coding Agents: What's Working and What's Not -&gt; Stop Making AI Guess: When Your Codebase Becomes the Spec</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fireside chat - When coding agents are the user? -&gt; East Village</t>
+          <t xml:space="preserve">Shipping Faster with AI Coding Agents: What's Working and What's Not -&gt; Union Square</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fireside chat - When coding agents are the user? -&gt; East Village</t>
+          <t xml:space="preserve">Shipping Faster with AI Coding Agents: What's Working and What's Not -&gt; Union Square</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5510,17 +5510,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 1 min to 28 St (N/Q/R/W); subway 13 min; walk 1 min from Astor Pl (4/6); includes 5 min buffer.</t>
+          <t xml:space="preserve">Walk 0 min to Prince St (N/Q/R/W); subway 4 min; walk 0 min from 14 St-Union Sq (N/Q/R/W); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t xml:space="preserve">N 28 St to 14 St-Union Sq; 4 14 St-Union Sq to Astor Pl</t>
+          <t xml:space="preserve">N Prince St to 14 St-Union Sq</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Leave previous event 9 min before its scheduled end.</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/events/6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">https://partiful.com/e/X0u5GrmzvIUTrjoAOgVm</t>
         </is>
       </c>
     </row>
@@ -5562,22 +5562,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4664</t>
+          <t xml:space="preserve">TW-5204</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4664-REFERENCE</t>
+          <t xml:space="preserve">TW-5204-REFERENCE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">eSldi3iNIvAVo9utdd8S</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4664</t>
+          <t xml:space="preserve">5204</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5592,42 +5592,42 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 18:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:30</t>
+          <t xml:space="preserve">2026-06-04 20:30</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 18:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:30</t>
+          <t xml:space="preserve">2026-06-04 20:30</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4664] [PENDING PRIMARY] MCP in the Wild: Panel &amp; Night of Networking</t>
+          <t xml:space="preserve">[TW-5204] [PENDING BACKUP] From Prediction Markets to Predictive Intelligence Systems</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">East Village</t>
+          <t xml:space="preserve">Financial District</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astor Place, New York, NY</t>
+          <t xml:space="preserve">Wall St, New York, NY</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5667,49 +5667,49 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">89</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/events/6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">https://partiful.com/e/eSldi3iNIvAVo9utdd8S</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4664</t>
+          <t xml:space="preserve">TW-5231</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4664-SCHEDULE</t>
+          <t xml:space="preserve">TW-5231-REFERENCE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">idltitmjA4ZzL9IuK0Y6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4664</t>
+          <t xml:space="preserve">5231</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5724,42 +5724,42 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">apply</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 18:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:30</t>
+          <t xml:space="preserve">2026-06-04 21:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 18:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:30</t>
+          <t xml:space="preserve">2026-06-04 21:00</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4664] [PENDING] MCP in the Wild: Panel &amp; Night of Networking</t>
+          <t xml:space="preserve">[TW-5231] [PENDING CURATED] AI BUILDERS DINNER</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">East Village</t>
+          <t xml:space="preserve">Flatiron, Manhattan, New York, NY</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astor Place, New York, NY</t>
+          <t xml:space="preserve">23rd Street and Broadway, New York, NY</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5799,49 +5799,49 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/events/6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">https://partiful.com/e/idltitmjA4ZzL9IuK0Y6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4197</t>
+          <t xml:space="preserve">TW-5114</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4197-REFERENCE</t>
+          <t xml:space="preserve">TW-5114-SCHEDULE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">UhyErPPxuo2vELIutdGj</t>
+          <t xml:space="preserve">X0u5GrmzvIUTrjoAOgVm</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197</t>
+          <t xml:space="preserve">5114</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5861,37 +5861,37 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 19:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 21:00</t>
+          <t xml:space="preserve">2026-06-04 20:45</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 19:00</t>
+          <t xml:space="preserve">2026-06-04 19:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 21:00</t>
+          <t xml:space="preserve">2026-06-04 20:45</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4197] [PENDING CURATED] The Tech Leaders Suite</t>
+          <t xml:space="preserve">[TW-5114] [REG] Stop Making AI Guess: When Your Codebase Becomes the Spec</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brooklyn</t>
+          <t xml:space="preserve">Union Square</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barclays Center, Brooklyn, NY</t>
+          <t xml:space="preserve">Union Square, Manhattan, New York, NY</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve">Registered direct. This is the Thursday anchor unless a substantially better curated dinner approves. Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5941,144 +5941,144 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/UhyErPPxuo2vELIutdGj?</t>
+          <t xml:space="preserve">https://partiful.com/e/X0u5GrmzvIUTrjoAOgVm</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">schedule</t>
+          <t xml:space="preserve">reference</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4664</t>
+          <t xml:space="preserve">TW-5207</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-20260603-TRAVEL-HOME</t>
+          <t xml:space="preserve">TW-5207-REFERENCE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">ed2EFWip0do9OuYmVPZI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">5207</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">event</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">registered</t>
+          <t xml:space="preserve">applied</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel</t>
+          <t xml:space="preserve">backup</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:30</t>
+          <t xml:space="preserve">2026-06-04 20:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:50</t>
+          <t xml:space="preserve">2026-06-04 21:30</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:30</t>
+          <t xml:space="preserve">2026-06-04 20:00</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-03 20:50</t>
+          <t xml:space="preserve">2026-06-04 21:30</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-20260603-TRAVEL-HOME] MCP in the Wild: Panel &amp; Night of Networking -&gt; FiDi home base</t>
+          <t xml:space="preserve">[TW-5207] [PENDING BACKUP] Free Phos, Real Convos. Agents in your DMs</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCP in the Wild: Panel &amp; Night of Networking -&gt; FiDi home base</t>
+          <t xml:space="preserve">Flatiron</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCP in the Wild: Panel &amp; Night of Networking -&gt; FiDi home base</t>
+          <t xml:space="preserve">Pho Dragon Restaurant, 47 W 14th St, New York, NY 10011</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">exact_from_partiful_maps</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">subway+walk</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 1 min to Astor Pl (4/6); subway 14 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 Astor Pl to Wall St</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor delays possible</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none. Required follow questions answered truthfully as Not yet.</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">79</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/events/6ZuudQBBZXcMNjdMynJ2</t>
+          <t xml:space="preserve">https://partiful.com/e/ed2EFWip0do9OuYmVPZI</t>
         </is>
       </c>
     </row>
@@ -6090,17 +6090,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5372</t>
+          <t xml:space="preserve">TW-5114</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5372-TRAVEL-IN</t>
+          <t xml:space="preserve">TW-20260604-TRAVEL-HOME</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5K5c4eODrGPKME7or20H</t>
+          <t xml:space="preserve">X0u5GrmzvIUTrjoAOgVm</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6125,37 +6125,37 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 15:36</t>
+          <t xml:space="preserve">2026-06-04 20:45</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 16:00</t>
+          <t xml:space="preserve">2026-06-04 21:03</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 15:36</t>
+          <t xml:space="preserve">2026-06-04 20:45</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 16:00</t>
+          <t xml:space="preserve">2026-06-04 21:03</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5372-TRAVEL-IN] FiDi home base -&gt; Shipping Faster with AI Coding Agents: What's Working and What's Not</t>
+          <t xml:space="preserve">[TW-20260604-TRAVEL-HOME] Stop Making AI Guess: When Your Codebase Becomes the Spec -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FiDi home base -&gt; New York, NY</t>
+          <t xml:space="preserve">Stop Making AI Guess: When Your Codebase Becomes the Spec -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FiDi home base -&gt; New York, NY</t>
+          <t xml:space="preserve">Stop Making AI Guess: When Your Codebase Becomes the Spec -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 19 min; walk 0 min from Prince St (N/Q/R/W); includes 5 min buffer.</t>
+          <t xml:space="preserve">Walk 0 min to 14 St-Union Sq (N/Q/R/W); subway 13 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Wall St to Canal St; Q Canal St to Prince St</t>
+          <t xml:space="preserve">N 14 St-Union Sq to 14 St-Union Sq; 5 14 St-Union Sq to Wall St</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor delays possible</t>
+          <t xml:space="preserve">Normal service</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -6210,139 +6210,139 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/5K5c4eODrGPKME7or20H</t>
+          <t xml:space="preserve">https://partiful.com/e/X0u5GrmzvIUTrjoAOgVm</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5372</t>
+          <t xml:space="preserve">TW-5722</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5372-REFERENCE</t>
+          <t xml:space="preserve">TW-5722-TRAVEL-IN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5K5c4eODrGPKME7or20H</t>
+          <t xml:space="preserve">jkjGahQgmH9PLIxjfTFt</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 16:00</t>
+          <t xml:space="preserve">2026-06-05 16:22</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
+          <t xml:space="preserve">2026-06-05 17:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 16:00</t>
+          <t xml:space="preserve">2026-06-05 16:22</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
+          <t xml:space="preserve">2026-06-05 17:00</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5372] [PENDING PRIMARY] Shipping Faster with AI Coding Agents: What's Working and What's Not</t>
+          <t xml:space="preserve">[TW-5722-TRAVEL-IN] FiDi home base -&gt; Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">FiDi home base -&gt; Union Square</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
+          <t xml:space="preserve">FiDi home base -&gt; Union Square</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 29 min; walk 4 min from 14 St-Union Sq (N/Q/R/W); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2 Wall St to 23 St; N 23 St to 14 St-Union Sq</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Minor delays possible</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leave early if needed so you can make the registered 19:00 Stop Making AI Guess event. Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/5K5c4eODrGPKME7or20H</t>
+          <t xml:space="preserve">https://partiful.com/e/jkjGahQgmH9PLIxjfTFt</t>
         </is>
       </c>
     </row>
@@ -6354,22 +6354,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5372</t>
+          <t xml:space="preserve">TW-5722</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-5372-SCHEDULE</t>
+          <t xml:space="preserve">TW-5722-SCHEDULE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5K5c4eODrGPKME7or20H</t>
+          <t xml:space="preserve">jkjGahQgmH9PLIxjfTFt</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372</t>
+          <t xml:space="preserve">5722</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6389,42 +6389,42 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 16:00</t>
+          <t xml:space="preserve">2026-06-05 17:00</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 18:51</t>
+          <t xml:space="preserve">2026-06-05 20:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 16:00</t>
+          <t xml:space="preserve">2026-06-05 17:00</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
+          <t xml:space="preserve">2026-06-05 20:00</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-5372] [PENDING] Shipping Faster with AI Coding Agents: What's Working and What's Not</t>
+          <t xml:space="preserve">[TW-5722] [PENDING] Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">Union Square</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
+          <t xml:space="preserve">Union Square Park, 201 Park Ave S, New York, NY 10003</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
+          <t xml:space="preserve">exact_from_partiful_maps</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -6454,27 +6454,27 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leave early if needed so you can make the registered 19:00 Stop Making AI Guess event. Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none. Route calendar shortens this from the event's scheduled 19:00 end; leave 9 min early for transit.</t>
+          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/5K5c4eODrGPKME7or20H</t>
+          <t xml:space="preserve">https://partiful.com/e/jkjGahQgmH9PLIxjfTFt</t>
         </is>
       </c>
     </row>
@@ -6486,22 +6486,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4191</t>
+          <t xml:space="preserve">TW-250</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4191-REFERENCE</t>
+          <t xml:space="preserve">TW-250-REFERENCE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6BlGFmwIdpyndqyLYS2v</t>
+          <t xml:space="preserve">kvGpuFMeACW7ZWPYtxTP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4191</t>
+          <t xml:space="preserve">250</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6516,42 +6516,42 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">apply</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 18:00</t>
+          <t xml:space="preserve">2026-06-05 18:00</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 20:00</t>
+          <t xml:space="preserve">2026-06-05 21:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 18:00</t>
+          <t xml:space="preserve">2026-06-05 18:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 20:00</t>
+          <t xml:space="preserve">2026-06-05 21:00</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4191] [PENDING BACKUP] Agents at Scale</t>
+          <t xml:space="preserve">[TW-250] [PENDING CURATED] YouCode AI Salon</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">SoHo</t>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring St and Broadway, New York, NY</t>
+          <t xml:space="preserve">Barclays Center, Brooklyn, NY</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6591,1874 +6591,158 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t xml:space="preserve">93</t>
+          <t xml:space="preserve">73</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://partiful.com/e/6BlGFmwIdpyndqyLYS2v?c=bv5YqCoL</t>
+          <t xml:space="preserve">https://partiful.com/e/kvGpuFMeACW7ZWPYtxTP</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">schedule</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4826</t>
+          <t xml:space="preserve">TW-5722</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TW-4826-REFERENCE</t>
+          <t xml:space="preserve">TW-20260605-TRAVEL-HOME</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">sGvp4VIr3KrGqRoWCKhV</t>
+          <t xml:space="preserve">jkjGahQgmH9PLIxjfTFt</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4826</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">applied</t>
+          <t xml:space="preserve">registered</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">backup</t>
+          <t xml:space="preserve">travel</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 18:00</t>
+          <t xml:space="preserve">2026-06-05 20:00</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 19:30</t>
+          <t xml:space="preserve">2026-06-05 20:22</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 18:00</t>
+          <t xml:space="preserve">2026-06-05 20:00</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04 19:30</t>
+          <t xml:space="preserve">2026-06-05 20:22</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TW-4826] [PENDING BACKUP] Steal These AI Workflows: Live Demos from NYC's Top AI Builders</t>
+          <t xml:space="preserve">[TW-20260605-TRAVEL-HOME] Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Union Square</t>
+          <t xml:space="preserve">Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Union Square E, New York, NY 10003</t>
+          <t xml:space="preserve">Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration -&gt; FiDi home base</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">subway+walk</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Walk 4 min to 14 St-Union Sq (N/Q/R/W); subway 13 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N 14 St-Union Sq to 14 St-Union Sq; 5 14 St-Union Sq to Wall St</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Normal service</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none. Secondary Google Form submitted for UbiquityOS Accolades build demo.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/sGvp4VIr3KrGqRoWCKhV</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reference</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-4183</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-4183-REFERENCE</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bETmU06uq4TtORng6I1l</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4183</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applied</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">apply</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 18:30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:30</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 18:30</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:30</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-4183] [PENDING CURATED] Engineering Leaders After Hours: A Build and Ship Cocktail Competition</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BarChef NYC, 21 W 35th St,, New York, NY</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BarChef NYC, 21 W 35th St,, New York, NY</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exact_from_signup_status</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/bETmU06uq4TtORng6I1l</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schedule</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5114</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5114-TRAVEL-IN</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">registered</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 18:51</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 18:51</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5114-TRAVEL-IN] Shipping Faster with AI Coding Agents: What's Working and What's Not -&gt; Stop Making AI Guess: When Your Codebase Becomes the Spec</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shipping Faster with AI Coding Agents: What's Working and What's Not -&gt; Union Square</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shipping Faster with AI Coding Agents: What's Working and What's Not -&gt; Union Square</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subway+walk</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Walk 0 min to Prince St (N/Q/R/W); subway 4 min; walk 0 min from 14 St-Union Sq (N/Q/R/W); includes 5 min buffer.</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N Prince St to 14 St-Union Sq</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Minor delays possible</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leave previous event 9 min before its scheduled end.</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reference</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5114</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5114-REFERENCE</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5114</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">registered</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">apply</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:45</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:45</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5114] [REG CURATED] Stop Making AI Guess: When Your Codebase Becomes the Spec</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square, Manhattan, New York, NY</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Registered direct. This is the Thursday anchor unless a substantially better curated dinner approves. Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reference</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5204</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5204-REFERENCE</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eSldi3iNIvAVo9utdd8S</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5204</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applied</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backup</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:30</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:30</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5204] [PENDING BACKUP] From Prediction Markets to Predictive Intelligence Systems</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Financial District</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wall St, New York, NY</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/eSldi3iNIvAVo9utdd8S</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reference</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5231</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5231-REFERENCE</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">idltitmjA4ZzL9IuK0Y6</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5231</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applied</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">apply</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:00</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:00</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5231] [PENDING CURATED] AI BUILDERS DINNER</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flatiron, Manhattan, New York, NY</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23rd Street and Broadway, New York, NY</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/idltitmjA4ZzL9IuK0Y6</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schedule</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5114</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5114-SCHEDULE</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5114</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">registered</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">apply</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:45</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 19:00</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:45</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5114] [REG] Stop Making AI Guess: When Your Codebase Becomes the Spec</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square, Manhattan, New York, NY</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Registered direct. This is the Thursday anchor unless a substantially better curated dinner approves. Registered; monitor for updates Submitted via Partiful API; rsvpStatus=GOING; count=2; plusOne=TBD.</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reference</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5207</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5207-REFERENCE</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ed2EFWip0do9OuYmVPZI</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5207</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applied</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backup</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:00</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:30</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:00</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:30</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5207] [PENDING BACKUP] Free Phos, Real Convos. Agents in your DMs</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flatiron</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pho Dragon Restaurant, 47 W 14th St, New York, NY 10011</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none. Required follow questions answered truthfully as Not yet.</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/ed2EFWip0do9OuYmVPZI</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schedule</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5114</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-20260604-TRAVEL-HOME</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">registered</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:45</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:03</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 20:45</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04 21:03</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-20260604-TRAVEL-HOME] Stop Making AI Guess: When Your Codebase Becomes the Spec -&gt; FiDi home base</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stop Making AI Guess: When Your Codebase Becomes the Spec -&gt; FiDi home base</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stop Making AI Guess: When Your Codebase Becomes the Spec -&gt; FiDi home base</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subway+walk</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Walk 0 min to 14 St-Union Sq (N/Q/R/W); subway 13 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N 14 St-Union Sq to 14 St-Union Sq; 5 14 St-Union Sq to Wall St</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Normal service</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/X0u5GrmzvIUTrjoAOgVm</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schedule</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5722</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5722-TRAVEL-IN</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jkjGahQgmH9PLIxjfTFt</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">registered</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 16:22</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 17:00</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 16:22</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 17:00</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5722-TRAVEL-IN] FiDi home base -&gt; Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FiDi home base -&gt; Union Square</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FiDi home base -&gt; Union Square</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subway+walk</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Walk 0 min to Wall St (2/3); subway 29 min; walk 4 min from 14 St-Union Sq (N/Q/R/W); includes 5 min buffer.</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 Wall St to 23 St; N 23 St to 14 St-Union Sq</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Minor delays possible</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/jkjGahQgmH9PLIxjfTFt</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reference</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5722</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5722-REFERENCE</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jkjGahQgmH9PLIxjfTFt</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5722</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applied</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">primary</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 17:00</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:00</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 17:00</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:00</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5722] [PENDING PRIMARY] Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square Park, 201 Park Ave S, New York, NY 10003</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/jkjGahQgmH9PLIxjfTFt</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schedule</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5722</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5722-SCHEDULE</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jkjGahQgmH9PLIxjfTFt</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5722</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applied</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">primary</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 17:00</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:00</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 17:00</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:00</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-5722] [PENDING] Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Union Square Park, 201 Park Ave S, New York, NY 10003</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">exact_from_partiful_maps</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/jkjGahQgmH9PLIxjfTFt</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reference</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-250</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-250-REFERENCE</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kvGpuFMeACW7ZWPYtxTP</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applied</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">apply</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 18:00</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 21:00</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 18:00</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 21:00</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-250] [PENDING CURATED] YouCode AI Salon</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New York, NY</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Barclays Center, Brooklyn, NY</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">approx_neighborhood_hidden</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wait for host approval Submitted via Partiful API; rsvpStatus=PENDING_APPROVAL; count=1; plusOne=none.</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://partiful.com/e/kvGpuFMeACW7ZWPYtxTP</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schedule</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-5722</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TW-20260605-TRAVEL-HOME</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jkjGahQgmH9PLIxjfTFt</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">registered</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:00</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:22</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:00</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-05 20:22</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[TW-20260605-TRAVEL-HOME] Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration -&gt; FiDi home base</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration -&gt; FiDi home base</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bare Metal Happy Hour: Autonomous Systems &amp; Agent Fleet Orchestration -&gt; FiDi home base</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subway+walk</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Walk 4 min to 14 St-Union Sq (N/Q/R/W); subway 13 min; walk 0 min from Wall St (2/3); includes 5 min buffer.</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N 14 St-Union Sq to 14 St-Union Sq; 5 14 St-Union Sq to Wall St</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Normal service</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
         <is>
           <t xml:space="preserve">https://partiful.com/e/jkjGahQgmH9PLIxjfTFt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z64"/>
+  <autoFilter ref="A1:Z51"/>
 </worksheet>
 </file>